--- a/CanyonRidge/supply/Canyon_Ridge__Supply_Chart.xlsx
+++ b/CanyonRidge/supply/Canyon_Ridge__Supply_Chart.xlsx
@@ -895,7 +895,7 @@
         <v>0.974453</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>2213</v>
+        <v>2147.615759341101</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
     <row r="24">
       <c r="B24" s="28" t="inlineStr">
         <is>
-          <t>* 5-Mile radius. Rent ($) = market asking. Proximity (mi) = straight-line distance from the subject. Est. Delivery drives the Supply &amp; Absorption tab's per-window supply (edit it there or here — they are linked). See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
+          <t>* 5-Mile radius. Rent ($) = HelloData mix-weighted asking where covered, else market asking (CoStar). Proximity (mi) = straight-line distance from the subject. Est. Delivery drives the Supply &amp; Absorption tab's per-window supply (edit it there or here — they are linked). See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
         </is>
       </c>
     </row>
@@ -2185,10 +2185,10 @@
         <v>1953</v>
       </c>
       <c r="H23" s="48" t="n">
-        <v>1977</v>
+        <v>1944</v>
       </c>
       <c r="I23" s="48">
-        <f>IFERROR('Cash Flow (Annual)'!$F$4,2136)</f>
+        <f>IFERROR('Cash Flow (Annual)'!$F$4,2029)</f>
         <v/>
       </c>
       <c r="J23" s="49">
@@ -2294,10 +2294,10 @@
         <v>1953</v>
       </c>
       <c r="H25" s="48" t="n">
-        <v>1823</v>
+        <v>1795</v>
       </c>
       <c r="I25" s="48">
-        <f>IFERROR('Cash Flow (Annual)'!$F$5,2018)</f>
+        <f>IFERROR('Cash Flow (Annual)'!$F$5,1924)</f>
         <v/>
       </c>
       <c r="J25" s="49">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="E66" s="71" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>HD</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="E67" s="71" t="inlineStr">
         <is>
-          <t>HD occ + CoStar rents</t>
+          <t>HD</t>
         </is>
       </c>
     </row>
@@ -3806,8 +3806,12 @@
       <c r="L5" s="74" t="n">
         <v>2303</v>
       </c>
-      <c r="M5" s="74" t="n"/>
-      <c r="N5" s="74" t="n"/>
+      <c r="M5" s="74" t="n">
+        <v>2147.615759341101</v>
+      </c>
+      <c r="N5" s="74" t="n">
+        <v>2147.615759341101</v>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>

--- a/CanyonRidge/supply/Canyon_Ridge__Supply_Chart.xlsx
+++ b/CanyonRidge/supply/Canyon_Ridge__Supply_Chart.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="0.0&quot; mi&quot;;;&quot;—&quot;"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,11 +122,6 @@
     <font>
       <name val="Calibri"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="FFC00000"/>
       <sz val="8"/>
     </font>
     <font>
@@ -230,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -411,10 +406,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -870,7 +864,7 @@
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>STABILIZED / STABILIZING (4 properties, 367 units)</t>
+          <t>STABILIZED / STABILIZING (5 properties, 492 units)</t>
         </is>
       </c>
     </row>
@@ -972,37 +966,41 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Mesa Pointe Apartments</t>
+          <t>The Mill at Loggers Creek</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Q3 2024</t>
+          <t>Q2 2024</t>
         </is>
       </c>
       <c r="F8" s="9" t="n">
-        <v>1</v>
+        <v>0.912</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>1647</v>
+        <v>2148.791666666667</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Rre Mesa Pointe Llc</t>
+          <t>Baron Properties</t>
         </is>
       </c>
       <c r="I8" s="11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Low-Rise</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n"/>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>Occ: CoStar 91% vs RealPage 94%</t>
+        </is>
+      </c>
       <c r="M8">
         <f>IFERROR(VALUE(RIGHT(E8,4))*4+MATCH(LEFT(E8,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
@@ -1014,30 +1012,30 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Veazey Apartments</t>
+          <t>Mesa Pointe Apartments</t>
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Q4 2024</t>
+          <t>Q3 2024</t>
         </is>
       </c>
       <c r="F9" s="9" t="n">
-        <v>0.971429</v>
+        <v>1</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>1547</v>
+        <v>1647</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Conrad J Frank</t>
+          <t>Rre Mesa Pointe Llc</t>
         </is>
       </c>
       <c r="I9" s="11" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -1050,104 +1048,108 @@
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>UNDER CONSTRUCTION (1 properties, 27 units)</t>
-        </is>
+    <row r="10">
+      <c r="B10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Veazey Apartments</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Q4 2024</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>0.971429</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>1547</v>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Conrad J Frank</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Low-Rise</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="n"/>
+      <c r="M10">
+        <f>IFERROR(VALUE(RIGHT(E10,4))*4+MATCH(LEFT(E10,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>UNDER CONSTRUCTION (1 properties, 30 units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>737 ParkCenter</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="D13" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Q3 2027</t>
         </is>
       </c>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t>Scott G Kimball</t>
         </is>
       </c>
-      <c r="I12" s="19" t="n">
+      <c r="I13" s="19" t="n">
         <v>3.2</v>
       </c>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>Low-Rise</t>
         </is>
       </c>
-      <c r="K12" s="15" t="n"/>
-      <c r="M12">
-        <f>IFERROR(VALUE(RIGHT(E12,4))*4+MATCH(LEFT(E12,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>PROPOSED (7 properties, 1,901 units)</t>
-        </is>
+      <c r="K13" s="15" t="inlineStr">
+        <is>
+          <t>Diligence: under construction</t>
+        </is>
+      </c>
+      <c r="M13">
+        <f>IFERROR(VALUE(RIGHT(E13,4))*4+MATCH(LEFT(E13,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>The Ranahan</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="n">
-        <v>138</v>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>Q4 2028</t>
-        </is>
-      </c>
-      <c r="F15" s="25" t="n"/>
-      <c r="G15" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" s="23" t="inlineStr">
-        <is>
-          <t>Dave Evans Construction</t>
-        </is>
-      </c>
-      <c r="I15" s="27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J15" s="22" t="inlineStr">
-        <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
-      <c r="K15" s="23" t="n"/>
-      <c r="M15">
-        <f>IFERROR(VALUE(RIGHT(E15,4))*4+MATCH(LEFT(E15,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>PROPOSED (6 properties, 1,788 units)</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1156,15 +1158,15 @@
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>Vista Point</t>
+          <t>Seasons on the Bench</t>
         </is>
       </c>
       <c r="D16" s="24" t="n">
-        <v>893</v>
+        <v>300</v>
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q3 2028</t>
         </is>
       </c>
       <c r="F16" s="25" t="n"/>
@@ -1179,16 +1181,16 @@
         </is>
       </c>
       <c r="I16" s="27" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J16" s="22" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M16">
@@ -1202,15 +1204,15 @@
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>Seasons on the Bench</t>
+          <t>The Ranahan</t>
         </is>
       </c>
       <c r="D17" s="24" t="n">
-        <v>358</v>
+        <v>138</v>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q4 2028</t>
         </is>
       </c>
       <c r="F17" s="25" t="n"/>
@@ -1221,20 +1223,20 @@
       </c>
       <c r="H17" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Dave Evans Construction</t>
         </is>
       </c>
       <c r="I17" s="27" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J17" s="22" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K17" s="23" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
       <c r="M17">
@@ -1248,11 +1250,11 @@
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>1519 South Londoner Avenue</t>
+          <t>Vista Point</t>
         </is>
       </c>
       <c r="D18" s="24" t="n">
-        <v>189</v>
+        <v>892</v>
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
@@ -1271,16 +1273,16 @@
         </is>
       </c>
       <c r="I18" s="27" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J18" s="22" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M18">
@@ -1294,11 +1296,11 @@
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>3300 South Vista Avenue</t>
+          <t>1519 South Londoner Avenue</t>
         </is>
       </c>
       <c r="D19" s="24" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
@@ -1317,16 +1319,16 @@
         </is>
       </c>
       <c r="I19" s="27" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J19" s="22" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K19" s="23" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M19">
@@ -1340,11 +1342,11 @@
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>Station Village</t>
+          <t>3300 South Vista Avenue</t>
         </is>
       </c>
       <c r="D20" s="24" t="n">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
@@ -1359,20 +1361,20 @@
       </c>
       <c r="H20" s="23" t="inlineStr">
         <is>
-          <t>Privately Owned</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I20" s="27" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="J20" s="22" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M20">
@@ -1386,11 +1388,11 @@
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>Harris Ranch East</t>
+          <t>Station Village</t>
         </is>
       </c>
       <c r="D21" s="24" t="n">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
@@ -1405,20 +1407,20 @@
       </c>
       <c r="H21" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Privately Owned</t>
         </is>
       </c>
       <c r="I21" s="27" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J21" s="22" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K21" s="23" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M21">
@@ -1436,11 +1438,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="C11:K11"/>
+    <mergeCell ref="C15:K15"/>
     <mergeCell ref="C5:K5"/>
     <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C14:K14"/>
     <mergeCell ref="B24:K24"/>
+    <mergeCell ref="C12:K12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1557,15 +1559,15 @@
         </is>
       </c>
       <c r="R5" s="35">
-        <f>'Competitive Analysis'!C12</f>
+        <f>'Competitive Analysis'!C13</f>
         <v/>
       </c>
       <c r="S5" s="36">
-        <f>'Competitive Analysis'!D12</f>
+        <f>'Competitive Analysis'!D13</f>
         <v/>
       </c>
       <c r="T5" s="37">
-        <f>'Competitive Analysis'!E12</f>
+        <f>'Competitive Analysis'!E13</f>
         <v/>
       </c>
       <c r="V5">
@@ -1649,7 +1651,7 @@
         </is>
       </c>
       <c r="S9" s="36" t="n">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="T9" s="40" t="inlineStr"/>
       <c r="U9" s="40" t="inlineStr">
@@ -1690,9 +1692,13 @@
         </is>
       </c>
       <c r="S10" s="36" t="n">
-        <v>358</v>
-      </c>
-      <c r="T10" s="40" t="inlineStr"/>
+        <v>300</v>
+      </c>
+      <c r="T10" s="40" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
       <c r="U10" s="40" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -1755,7 +1761,7 @@
         </is>
       </c>
       <c r="S12" s="36" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="T12" s="40" t="inlineStr"/>
       <c r="U12" s="40" t="inlineStr">
@@ -1815,7 +1821,7 @@
         </is>
       </c>
       <c r="S14" s="36" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="T14" s="40" t="inlineStr"/>
       <c r="U14" s="40" t="inlineStr">
@@ -1836,34 +1842,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="14.4" customHeight="1">
-      <c r="R15" s="35" t="inlineStr">
-        <is>
-          <t>Harris Ranch East</t>
-        </is>
-      </c>
-      <c r="S15" s="36" t="n">
-        <v>59</v>
-      </c>
-      <c r="T15" s="40" t="inlineStr"/>
-      <c r="U15" s="40" t="inlineStr">
-        <is>
-          <t>Bear only</t>
-        </is>
-      </c>
-      <c r="V15">
-        <f>IFERROR(VALUE(RIGHT(T15,4))*4+MATCH(LEFT(T15,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W15">
-        <f>IF(V15="","",IF(V15&lt;=$Z$1,0,MAX(1,INT((V15-$Z$2)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>IF(U15="All",1,IF(U15="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U15="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
-        <v/>
-      </c>
-    </row>
+    <row r="15" ht="14.4" customHeight="1"/>
     <row r="16" ht="14.4" customHeight="1"/>
     <row r="17" ht="14.4" customHeight="1">
       <c r="B17" s="30" t="inlineStr">
@@ -2027,27 +2006,27 @@
         <v/>
       </c>
       <c r="J19" s="45">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,1)+SUMIFS($S$9:$S$15,$W$9:$W$15,1,$X$9:$X$15,1)</f>
+        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,1)+SUMIFS($S$9:$S$14,$W$9:$W$14,1,$X$9:$X$14,1)</f>
         <v/>
       </c>
       <c r="K19" s="45">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,2)+SUMIFS($S$9:$S$15,$W$9:$W$15,2,$X$9:$X$15,1)</f>
+        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,2)+SUMIFS($S$9:$S$14,$W$9:$W$14,2,$X$9:$X$14,1)</f>
         <v/>
       </c>
       <c r="L19" s="45">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,3)+SUMIFS($S$9:$S$15,$W$9:$W$15,3,$X$9:$X$15,1)</f>
+        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,3)+SUMIFS($S$9:$S$14,$W$9:$W$14,3,$X$9:$X$14,1)</f>
         <v/>
       </c>
       <c r="M19" s="45">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,4)+SUMIFS($S$9:$S$15,$W$9:$W$15,4,$X$9:$X$15,1)</f>
+        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,4)+SUMIFS($S$9:$S$14,$W$9:$W$14,4,$X$9:$X$14,1)</f>
         <v/>
       </c>
       <c r="N19" s="45">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,5)+SUMIFS($S$9:$S$15,$W$9:$W$15,5,$X$9:$X$15,1)</f>
+        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,5)+SUMIFS($S$9:$S$14,$W$9:$W$14,5,$X$9:$X$14,1)</f>
         <v/>
       </c>
       <c r="O19" s="45">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,6)+SUMIFS($S$9:$S$15,$W$9:$W$15,6,$X$9:$X$15,1)</f>
+        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,6)+SUMIFS($S$9:$S$14,$W$9:$W$14,6,$X$9:$X$14,1)</f>
         <v/>
       </c>
     </row>
@@ -3425,7 +3404,7 @@
       </c>
       <c r="E68" s="71" t="inlineStr">
         <is>
-          <t>27 / 27</t>
+          <t>30 / 27</t>
         </is>
       </c>
     </row>
@@ -3451,9 +3430,9 @@
       </c>
     </row>
     <row r="72" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B72" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    -Y2: roster (CoStar-tracked) 46 vs CoStar 178   (+132 sub-50/unnamed)</t>
+      <c r="B72" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -Y2: roster (CoStar-tracked) 171 vs CoStar 178   (+7 sub-50/unnamed)</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3467,7 @@
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Bear,Base,Bull"</formula1>
     </dataValidation>
-    <dataValidation sqref="U9 U10 U11 U12 U13 U14 U15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U9 U10 U11 U12 U13 U14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Bear only,Bear+Base,All,None"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3637,17 +3616,17 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="H2" s="73" t="n">
+      <c r="H2" s="72" t="n">
         <v>0.971429</v>
       </c>
-      <c r="I2" s="73" t="n"/>
-      <c r="J2" s="73" t="n"/>
-      <c r="K2" s="74" t="n">
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="72" t="n"/>
+      <c r="K2" s="73" t="n">
         <v>1547</v>
       </c>
-      <c r="L2" s="74" t="n"/>
-      <c r="M2" s="74" t="n"/>
-      <c r="N2" s="74" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -3687,15 +3666,15 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="73" t="n"/>
-      <c r="J3" s="73" t="n"/>
-      <c r="K3" s="74" t="n">
+      <c r="H3" s="72" t="n"/>
+      <c r="I3" s="72" t="n"/>
+      <c r="J3" s="72" t="n"/>
+      <c r="K3" s="73" t="n">
         <v>1647</v>
       </c>
-      <c r="L3" s="74" t="n"/>
-      <c r="M3" s="74" t="n"/>
-      <c r="N3" s="74" t="n"/>
+      <c r="L3" s="73" t="n"/>
+      <c r="M3" s="73" t="n"/>
+      <c r="N3" s="73" t="n"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -3706,23 +3685,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>The Betty</t>
+          <t>The Mill at Loggers Creek</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2550 W Targee St</t>
+          <t>1250 S Division Ave</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c r="D4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Q4 2023</t>
+          <t>Q2 2024</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3735,21 +3714,25 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="H4" s="73" t="n">
-        <v>0.934783</v>
-      </c>
-      <c r="I4" s="73" t="n">
-        <v>0.961</v>
-      </c>
-      <c r="J4" s="73" t="n"/>
-      <c r="K4" s="74" t="n">
-        <v>1577</v>
-      </c>
-      <c r="L4" s="74" t="n">
-        <v>1273</v>
-      </c>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="74" t="n"/>
+      <c r="H4" s="72" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="I4" s="72" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="J4" s="72" t="n"/>
+      <c r="K4" s="73" t="n">
+        <v>2096</v>
+      </c>
+      <c r="L4" s="73" t="n">
+        <v>2150</v>
+      </c>
+      <c r="M4" s="73" t="n">
+        <v>2148.791666666667</v>
+      </c>
+      <c r="N4" s="73" t="n">
+        <v>2129.791666666667</v>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -3757,30 +3740,30 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Occ: CoStar 93% vs RealPage 96%; Rent: CoStar ask $1,577 vs RealPage eff $1,273</t>
+          <t>Occ: CoStar 91% vs RealPage 94%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>The Timbers at Harris Ranch</t>
+          <t>The Betty</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3469 S Old Hickory Way</t>
+          <t>2550 W Targee St</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>274</v>
+        <v>46</v>
       </c>
       <c r="D5" t="n">
         <v>2023</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Q2 2023</t>
+          <t>Q4 2023</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3793,25 +3776,21 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="H5" s="73" t="n">
-        <v>0.974453</v>
-      </c>
-      <c r="I5" s="73" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="J5" s="73" t="n"/>
-      <c r="K5" s="74" t="n">
-        <v>2213</v>
-      </c>
-      <c r="L5" s="74" t="n">
-        <v>2303</v>
-      </c>
-      <c r="M5" s="74" t="n">
-        <v>2147.615759341101</v>
-      </c>
-      <c r="N5" s="74" t="n">
-        <v>2147.615759341101</v>
-      </c>
+      <c r="H5" s="72" t="n">
+        <v>0.934783</v>
+      </c>
+      <c r="I5" s="72" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="J5" s="72" t="n"/>
+      <c r="K5" s="73" t="n">
+        <v>1577</v>
+      </c>
+      <c r="L5" s="73" t="n">
+        <v>1273</v>
+      </c>
+      <c r="M5" s="73" t="n"/>
+      <c r="N5" s="73" t="n"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -3819,155 +3798,193 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Year built: 2023/2024; Occ: CoStar 97% vs RealPage 100%</t>
+          <t>Occ: CoStar 93% vs RealPage 96%; Rent: CoStar ask $1,577 vs RealPage eff $1,273</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>737 ParkCenter</t>
+          <t>The Timbers at Harris Ranch</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>787 E Parkcenter Blvd</t>
+          <t>3469 S Old Hickory Way</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>274</v>
       </c>
       <c r="D6" t="n">
-        <v>2027</v>
+        <v>2023</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Q3 2027</t>
+          <t>Q2 2023</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CoStar property analytics</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNDER CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="H6" s="73" t="n"/>
-      <c r="I6" s="73" t="n"/>
-      <c r="J6" s="73" t="n"/>
-      <c r="K6" s="74" t="n"/>
-      <c r="L6" s="74" t="n"/>
-      <c r="M6" s="74" t="n"/>
-      <c r="N6" s="74" t="n"/>
+          <t>STABILIZED / STABILIZING</t>
+        </is>
+      </c>
+      <c r="H6" s="72" t="n">
+        <v>0.974453</v>
+      </c>
+      <c r="I6" s="72" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="J6" s="72" t="n"/>
+      <c r="K6" s="73" t="n">
+        <v>2213</v>
+      </c>
+      <c r="L6" s="73" t="n">
+        <v>2303</v>
+      </c>
+      <c r="M6" s="73" t="n">
+        <v>2147.615759341101</v>
+      </c>
+      <c r="N6" s="73" t="n">
+        <v>2147.615759341101</v>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>CoStar</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
+          <t>CoStar+RealPage</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Year built: 2023/2024; Occ: CoStar 97% vs RealPage 100%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>The Ranahan</t>
+          <t>737 ParkCenter</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4227 E Brightside St</t>
+          <t>787 E Parkcenter Blvd</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>138</v>
+        <v>30</v>
       </c>
       <c r="D7" t="n">
         <v>2027</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-      <c r="H7" s="73" t="n"/>
-      <c r="I7" s="73" t="n"/>
-      <c r="J7" s="73" t="n"/>
-      <c r="K7" s="74" t="n"/>
-      <c r="L7" s="74" t="n"/>
-      <c r="M7" s="74" t="n"/>
-      <c r="N7" s="74" t="n"/>
+          <t>UNDER CONSTRUCTION</t>
+        </is>
+      </c>
+      <c r="H7" s="72" t="n"/>
+      <c r="I7" s="72" t="n"/>
+      <c r="J7" s="72" t="n"/>
+      <c r="K7" s="73" t="n"/>
+      <c r="L7" s="73" t="n"/>
+      <c r="M7" s="73" t="n"/>
+      <c r="N7" s="73" t="n"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>CoStar</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Diligence: under construction</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3300 South Vista Avenue</t>
+          <t>The Ranahan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3300 S Vista Ave</t>
+          <t>4227 E Brightside St</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>180</v>
+        <v>138</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Q4 2028</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="H8" s="73" t="n"/>
-      <c r="I8" s="73" t="n"/>
-      <c r="J8" s="73" t="n"/>
-      <c r="K8" s="74" t="n"/>
-      <c r="L8" s="74" t="n"/>
-      <c r="M8" s="74" t="n"/>
-      <c r="N8" s="74" t="n"/>
+      <c r="H8" s="72" t="n"/>
+      <c r="I8" s="72" t="n"/>
+      <c r="J8" s="72" t="n"/>
+      <c r="K8" s="73" t="n"/>
+      <c r="L8" s="73" t="n"/>
+      <c r="M8" s="73" t="n"/>
+      <c r="N8" s="73" t="n"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>RealPage</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1519 South Londoner Avenue</t>
+          <t>Seasons on the Bench</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1519 S Londoner Ave</t>
+          <t>2521 W Victory Rd</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>189</v>
+        <v>300</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="H9" s="73" t="n"/>
-      <c r="I9" s="73" t="n"/>
-      <c r="J9" s="73" t="n"/>
-      <c r="K9" s="74" t="n"/>
-      <c r="L9" s="74" t="n"/>
-      <c r="M9" s="74" t="n"/>
-      <c r="N9" s="74" t="n"/>
+      <c r="H9" s="72" t="n"/>
+      <c r="I9" s="72" t="n"/>
+      <c r="J9" s="72" t="n"/>
+      <c r="K9" s="73" t="n"/>
+      <c r="L9" s="73" t="n"/>
+      <c r="M9" s="73" t="n"/>
+      <c r="N9" s="73" t="n"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -3975,36 +3992,36 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Station Village</t>
+          <t>3300 South Vista Avenue</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2350 W Kootenai St</t>
+          <t>3300 S Vista Ave</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="H10" s="73" t="n"/>
-      <c r="I10" s="73" t="n"/>
-      <c r="J10" s="73" t="n"/>
-      <c r="K10" s="74" t="n"/>
-      <c r="L10" s="74" t="n"/>
-      <c r="M10" s="74" t="n"/>
-      <c r="N10" s="74" t="n"/>
+      <c r="H10" s="72" t="n"/>
+      <c r="I10" s="72" t="n"/>
+      <c r="J10" s="72" t="n"/>
+      <c r="K10" s="73" t="n"/>
+      <c r="L10" s="73" t="n"/>
+      <c r="M10" s="73" t="n"/>
+      <c r="N10" s="73" t="n"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -4012,36 +4029,36 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Seasons on the Bench</t>
+          <t>1519 South Londoner Avenue</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2521 W Victory Rd</t>
+          <t>1519 S Londoner Ave</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>358</v>
+        <v>189</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="H11" s="73" t="n"/>
-      <c r="I11" s="73" t="n"/>
-      <c r="J11" s="73" t="n"/>
-      <c r="K11" s="74" t="n"/>
-      <c r="L11" s="74" t="n"/>
-      <c r="M11" s="74" t="n"/>
-      <c r="N11" s="74" t="n"/>
+      <c r="H11" s="72" t="n"/>
+      <c r="I11" s="72" t="n"/>
+      <c r="J11" s="72" t="n"/>
+      <c r="K11" s="73" t="n"/>
+      <c r="L11" s="73" t="n"/>
+      <c r="M11" s="73" t="n"/>
+      <c r="N11" s="73" t="n"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -4049,36 +4066,36 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Harris Ranch East</t>
+          <t>Station Village</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3201 S Council Spring Rd</t>
+          <t>2350 W Kootenai St</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="H12" s="73" t="n"/>
-      <c r="I12" s="73" t="n"/>
-      <c r="J12" s="73" t="n"/>
-      <c r="K12" s="74" t="n"/>
-      <c r="L12" s="74" t="n"/>
-      <c r="M12" s="74" t="n"/>
-      <c r="N12" s="74" t="n"/>
+      <c r="H12" s="72" t="n"/>
+      <c r="I12" s="72" t="n"/>
+      <c r="J12" s="72" t="n"/>
+      <c r="K12" s="73" t="n"/>
+      <c r="L12" s="73" t="n"/>
+      <c r="M12" s="73" t="n"/>
+      <c r="N12" s="73" t="n"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -4086,7 +4103,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
     </row>
@@ -4102,20 +4119,20 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="H13" s="73" t="n"/>
-      <c r="I13" s="73" t="n"/>
-      <c r="J13" s="73" t="n"/>
-      <c r="K13" s="74" t="n"/>
-      <c r="L13" s="74" t="n"/>
-      <c r="M13" s="74" t="n"/>
-      <c r="N13" s="74" t="n"/>
+      <c r="H13" s="72" t="n"/>
+      <c r="I13" s="72" t="n"/>
+      <c r="J13" s="72" t="n"/>
+      <c r="K13" s="73" t="n"/>
+      <c r="L13" s="73" t="n"/>
+      <c r="M13" s="73" t="n"/>
+      <c r="N13" s="73" t="n"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -4123,7 +4140,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H6"/>
+  <dimension ref="B2:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -4152,9 +4169,9 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="75" t="inlineStr">
-        <is>
-          <t>SHADOW SUPPLY (latent / untracked — watch list)</t>
+      <c r="B2" s="74" t="inlineStr">
+        <is>
+          <t>PIPELINE DILIGENCE</t>
         </is>
       </c>
     </row>
@@ -4198,68 +4215,349 @@
     <row r="4">
       <c r="B4" s="35" t="inlineStr">
         <is>
-          <t>Barber Valley SP-02 HDR block (Parkcenter)</t>
-        </is>
-      </c>
-      <c r="C4" s="76" t="n"/>
-      <c r="D4" s="76" t="n"/>
-      <c r="E4" s="35" t="n"/>
+          <t>Vista Point</t>
+        </is>
+      </c>
+      <c r="C4" s="75" t="inlineStr">
+        <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="D4" s="75" t="n"/>
+      <c r="E4" s="35" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
       <c r="F4" s="35" t="n"/>
       <c r="G4" s="35" t="inlineStr">
         <is>
-          <t>Land-use analysis site CR-51: 11.5 ac zoned SP-02 with High-Density Residential FLU inside the adopted Barber Valley Specific Plan; OUTSIDE the Airport Influence Area. Entitled/planned multifamily block, master-developed by Barber Valley Development (Harris Family LP); HDR blocks typically sold to merchant apartment developers. No active application found — the most apartment-competitive latent site in the 5-mi ring.</t>
+          <t>Welltower's 892-unit plan (25 units income-restricted at 100% AMI; 68-ft height exception) on the eastern Simunich site approved by Boise City Council Feb 2023. As of June 2026 the site remains an open field with Welltower still 'working through its development process' — no construction start, no defensible delivery date.</t>
         </is>
       </c>
       <c r="H4" s="35" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2021/11/12/harris-ranch-town-center/</t>
+          <t>https://boisedev.com/news/2023/02/15/simunich-welltower-approval-900-units/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="35" t="inlineStr">
         <is>
-          <t>McDonald Tract (S Oakland Ave)</t>
-        </is>
-      </c>
-      <c r="C5" s="76" t="n"/>
-      <c r="D5" s="76" t="n"/>
-      <c r="E5" s="35" t="n"/>
+          <t>Seasons on the Bench</t>
+        </is>
+      </c>
+      <c r="C5" s="75" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D5" s="75" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="E5" s="35" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
       <c r="F5" s="35" t="n"/>
       <c r="G5" s="35" t="inlineStr">
         <is>
-          <t>Land-use analysis site CR-57: 10.3 ac zoned R-3 (multifamily by-right) with Mixed Use FLU, outside the Airport Influence Area. Dormant — no application, listing, or news found; owner not published. By-right MF capacity makes it a genuine watch item despite no activity.</t>
+          <t>Original 354-unit MorganStonehill plan (approved 2023) never built and was superseded: Roundhouse re-pitched the site as 'Victory' — 300 garden-style units in 15 buildings at 2521/1251 W Victory Rd targeting a fall 2026 groundbreaking (June 2026 reporting). Q3 2028 = fall 2026 start + ~20 months.</t>
         </is>
       </c>
       <c r="H5" s="35" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/ID/Boise/1507-S-Oakland-Ave-83706/home/109555986</t>
+          <t>https://www.aol.com/news/300-apartments-coming-one-boise-100000368.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>East Columbia bench (Rush Valley / planned community)</t>
-        </is>
-      </c>
-      <c r="C6" s="76" t="n"/>
-      <c r="D6" s="76" t="n"/>
-      <c r="E6" s="35" t="n"/>
+          <t>3300 South Vista Avenue</t>
+        </is>
+      </c>
+      <c r="C6" s="75" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D6" s="75" t="n"/>
+      <c r="E6" s="35" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
       <c r="F6" s="35" t="n"/>
       <c r="G6" s="35" t="inlineStr">
         <is>
+          <t>Gardner Company phased redevelopment of three aging Vista Ave hotels: ~183 apartments (20% at 100% AMI via density bonus) plus a new 240-room hotel and Hindu temple; council denied the opposition appeal Oct 2023 and the ownership-fraud suit that stalled the project settled March 2025 — no vertical construction as of mid-2026.</t>
+        </is>
+      </c>
+      <c r="H6" s="35" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2025/03/15/hotel-settlement-vista/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>1519 South Londoner Avenue</t>
+        </is>
+      </c>
+      <c r="C7" s="75" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D7" s="75" t="n"/>
+      <c r="E7" s="35" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="35" t="inlineStr">
+        <is>
+          <t>Payette Forward (Austin TX) rezone for 189 units + ground-floor retail on ~6 ac along Highland St approved March 4 2025 (capped at 189 units). Londoner Neighborhood Assn suit dismissed Nov 2025 as untimely but appealed to the Idaho Supreme Court — entitlement upheld, litigation risk remains, no construction.</t>
+        </is>
+      </c>
+      <c r="H7" s="35" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2025/05/19/londoner-apartment-suit/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Station Village</t>
+        </is>
+      </c>
+      <c r="C8" s="75" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D8" s="75" t="n"/>
+      <c r="E8" s="35" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="n"/>
+      <c r="G8" s="35" t="inlineStr">
+        <is>
+          <t>Day Realty Co. plan for 86 units in six buildings + clubhouse at 2350 W Kootenai St; BoiseDev's project tracker has listed it 'on hold' since April 2021 with no subsequent approvals, permits, or news — stale entry, likely dead but unconfirmed. Undated, so not in the forecast. Sits on land-use developable parcel S1015325410.</t>
+        </is>
+      </c>
+      <c r="H8" s="35" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/project/station-village/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Harris Ranch East</t>
+        </is>
+      </c>
+      <c r="C9" s="75" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D9" s="75" t="n"/>
+      <c r="E9" s="35" t="inlineStr">
+        <is>
+          <t>not multifamily - 59 for-sale single-family ridgeline homes</t>
+        </is>
+      </c>
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="35" t="inlineStr">
+        <is>
+          <t>Boise Hunter Homes' 59 single-family ridgeline homes above East Junior High/Golden Dawn (22 ac developed, 93 ac open space); final plat worked through 2023 and foundations were being poured by early 2025 — for-sale SF product, not competitive multifamily supply.</t>
+        </is>
+      </c>
+      <c r="H9" s="35" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2021/04/13/harris-ranch-east/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>The Ranahan</t>
+        </is>
+      </c>
+      <c r="C10" s="75" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D10" s="75" t="n"/>
+      <c r="E10" s="35" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="35" t="inlineStr">
+        <is>
+          <t>Entitled 138-unit 4-story project at 4110 E Warm Springs Ave (Harris Ranch / Barber Valley, on land-use developable parcel R1719910020); appeared in city permit logs 2023 but the project/site is now marketed FOR SALE via KW Commercial — no construction, CoStar's Q4 2028 delivery is speculative.</t>
+        </is>
+      </c>
+      <c r="H10" s="35" t="inlineStr">
+        <is>
+          <t>https://realnex.com/listings/841866/the-ranahan</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>737 ParkCenter</t>
+        </is>
+      </c>
+      <c r="C11" s="75" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D11" s="75" t="n"/>
+      <c r="E11" s="35" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="35" t="inlineStr">
+        <is>
+          <t>Actual project is 787 E ParkCenter Blvd (Kimball family): 3-story mixed-use with 30 AGE-RESTRICTED (55+) apartments plus coffee shop/retail. City of Boise issued the $5.2M new-structure building permit 9/15/2025 — construction underway; CoStar's Q3 2027 delivery is plausible. Age restriction limits direct competitiveness.</t>
+        </is>
+      </c>
+      <c r="H11" s="35" t="inlineStr">
+        <is>
+          <t>https://www.djc.com/stories/images/permits/CityofBoise0901-0930.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="74" t="inlineStr">
+        <is>
+          <t>SHADOW SUPPLY (latent / untracked — watch list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="42" t="inlineStr">
+        <is>
+          <t>Property / Site</t>
+        </is>
+      </c>
+      <c r="C14" s="42" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="inlineStr">
+        <is>
+          <t>Est. Delivery</t>
+        </is>
+      </c>
+      <c r="E14" s="42" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F14" s="42" t="inlineStr">
+        <is>
+          <t>Leasing Pace</t>
+        </is>
+      </c>
+      <c r="G14" s="42" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="H14" s="42" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>Barber Valley SP-02 HDR block (Parkcenter)</t>
+        </is>
+      </c>
+      <c r="C15" s="75" t="n"/>
+      <c r="D15" s="75" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="35" t="inlineStr">
+        <is>
+          <t>Land-use analysis site CR-51: 11.5 ac zoned SP-02 with High-Density Residential FLU inside the adopted Barber Valley Specific Plan; OUTSIDE the Airport Influence Area. Entitled/planned multifamily block, master-developed by Barber Valley Development (Harris Family LP); HDR blocks typically sold to merchant apartment developers. No active application found — the most apartment-competitive latent site in the 5-mi ring.</t>
+        </is>
+      </c>
+      <c r="H15" s="35" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2021/11/12/harris-ranch-town-center/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>McDonald Tract (S Oakland Ave)</t>
+        </is>
+      </c>
+      <c r="C16" s="75" t="n"/>
+      <c r="D16" s="75" t="n"/>
+      <c r="E16" s="35" t="n"/>
+      <c r="F16" s="35" t="n"/>
+      <c r="G16" s="35" t="inlineStr">
+        <is>
+          <t>Land-use analysis site CR-57: 10.3 ac zoned R-3 (multifamily by-right) with Mixed Use FLU, outside the Airport Influence Area. Dormant — no application, listing, or news found; owner not published. By-right MF capacity makes it a genuine watch item despite no activity.</t>
+        </is>
+      </c>
+      <c r="H16" s="35" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/ID/Boise/1507-S-Oakland-Ave-83706/home/109555986</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>East Columbia bench (Rush Valley / planned community)</t>
+        </is>
+      </c>
+      <c r="C17" s="75" t="n"/>
+      <c r="D17" s="75" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="35" t="inlineStr">
+        <is>
           <t>Land-use analysis sites CR-2/CR-3/CR-5: ~1,700+ ac far-SE 'East Columbia' bench with Boise 'Planned Community' FLU — one of three strategic planning areas the city began studying Jan 2026. Rush Valley subdivision portion (Conger Group/DevCo) approved but capped and largely unbuilt; residential blocked by missing secondary fire access and landowner coordination (Simplot, Micron, Ball Ventures, Murgoitio). Long-horizon supply, not near-term.</t>
         </is>
       </c>
-      <c r="H6" s="35" t="inlineStr">
+      <c r="H17" s="35" t="inlineStr">
         <is>
           <t>https://boisedev.com/news/2026/01/28/southeast-boise-planning/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="B13:H13"/>
     <mergeCell ref="B2:H2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CanyonRidge/supply/Canyon_Ridge__Supply_Chart.xlsx
+++ b/CanyonRidge/supply/Canyon_Ridge__Supply_Chart.xlsx
@@ -777,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M24"/>
+  <dimension ref="B2:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1094,7 +1094,7 @@
       <c r="B12" s="12" t="n"/>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>UNDER CONSTRUCTION (1 properties, 30 units)</t>
+          <t>UNDER CONSTRUCTION (2 properties, 62 units)</t>
         </is>
       </c>
     </row>
@@ -1104,15 +1104,15 @@
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>737 ParkCenter</t>
+          <t>The Quarter at Harris Ranch</t>
         </is>
       </c>
       <c r="D13" s="16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Q3 2027</t>
+          <t>Q1 2027</t>
         </is>
       </c>
       <c r="F13" s="17" t="n"/>
@@ -1123,20 +1123,16 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>Scott G Kimball</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I13" s="19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J13" s="14" t="inlineStr">
-        <is>
-          <t>Low-Rise</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="J13" s="14" t="n"/>
       <c r="K13" s="15" t="inlineStr">
         <is>
-          <t>Diligence: under construction</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: under construction</t>
         </is>
       </c>
       <c r="M13">
@@ -1144,58 +1140,58 @@
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="20" t="n"/>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>PROPOSED (6 properties, 1,788 units)</t>
-        </is>
+    <row r="14">
+      <c r="B14" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>737 ParkCenter</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>Q3 2027</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>Scott G Kimball</t>
+        </is>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Low-Rise</t>
+        </is>
+      </c>
+      <c r="K14" s="15" t="inlineStr">
+        <is>
+          <t>Diligence: under construction</t>
+        </is>
+      </c>
+      <c r="M14">
+        <f>IFERROR(VALUE(RIGHT(E14,4))*4+MATCH(LEFT(E14,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>Seasons on the Bench</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="n">
-        <v>300</v>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="F16" s="25" t="n"/>
-      <c r="G16" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I16" s="27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J16" s="22" t="inlineStr">
-        <is>
-          <t>Garden</t>
-        </is>
-      </c>
-      <c r="K16" s="23" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
-        </is>
-      </c>
-      <c r="M16">
-        <f>IFERROR(VALUE(RIGHT(E16,4))*4+MATCH(LEFT(E16,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
+      <c r="B16" s="20" t="n"/>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>PROPOSED (7 properties, 1,982 units)</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1204,15 +1200,15 @@
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>The Ranahan</t>
+          <t>Seasons on the Bench</t>
         </is>
       </c>
       <c r="D17" s="24" t="n">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q3 2028</t>
         </is>
       </c>
       <c r="F17" s="25" t="n"/>
@@ -1223,20 +1219,20 @@
       </c>
       <c r="H17" s="23" t="inlineStr">
         <is>
-          <t>Dave Evans Construction</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I17" s="27" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J17" s="22" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K17" s="23" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M17">
@@ -1250,15 +1246,15 @@
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>Vista Point</t>
+          <t>The Ranahan</t>
         </is>
       </c>
       <c r="D18" s="24" t="n">
-        <v>892</v>
+        <v>138</v>
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q4 2028</t>
         </is>
       </c>
       <c r="F18" s="25" t="n"/>
@@ -1269,11 +1265,11 @@
       </c>
       <c r="H18" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Dave Evans Construction</t>
         </is>
       </c>
       <c r="I18" s="27" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J18" s="22" t="inlineStr">
         <is>
@@ -1282,7 +1278,7 @@
       </c>
       <c r="K18" s="23" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
       <c r="M18">
@@ -1296,11 +1292,11 @@
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>1519 South Londoner Avenue</t>
+          <t>Vista Point</t>
         </is>
       </c>
       <c r="D19" s="24" t="n">
-        <v>189</v>
+        <v>892</v>
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
@@ -1319,11 +1315,11 @@
         </is>
       </c>
       <c r="I19" s="27" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J19" s="22" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K19" s="23" t="inlineStr">
@@ -1342,11 +1338,11 @@
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>3300 South Vista Avenue</t>
+          <t>Kootenai &amp; Federal Way (Hawkins)</t>
         </is>
       </c>
       <c r="D20" s="24" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
@@ -1365,16 +1361,12 @@
         </is>
       </c>
       <c r="I20" s="27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J20" s="22" t="inlineStr">
-        <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
+        <v>4.1</v>
+      </c>
+      <c r="J20" s="22" t="n"/>
       <c r="K20" s="23" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
         </is>
       </c>
       <c r="M20">
@@ -1388,11 +1380,11 @@
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>Station Village</t>
+          <t>1519 South Londoner Avenue</t>
         </is>
       </c>
       <c r="D21" s="24" t="n">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
@@ -1407,11 +1399,11 @@
       </c>
       <c r="H21" s="23" t="inlineStr">
         <is>
-          <t>Privately Owned</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I21" s="27" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="J21" s="22" t="inlineStr">
         <is>
@@ -1428,8 +1420,100 @@
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="28" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>3300 South Vista Avenue</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="n">
+        <v>183</v>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F22" s="25" t="n"/>
+      <c r="G22" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+        </is>
+      </c>
+      <c r="M22">
+        <f>IFERROR(VALUE(RIGHT(E22,4))*4+MATCH(LEFT(E22,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>Station Village</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="n">
+        <v>86</v>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="n"/>
+      <c r="G23" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>Privately Owned</t>
+        </is>
+      </c>
+      <c r="I23" s="27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="K23" s="23" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+        </is>
+      </c>
+      <c r="M23">
+        <f>IFERROR(VALUE(RIGHT(E23,4))*4+MATCH(LEFT(E23,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>* 5-Mile radius. Rent ($) = HelloData mix-weighted asking where covered, else market asking (CoStar). Proximity (mi) = straight-line distance from the subject. Est. Delivery drives the Supply &amp; Absorption tab's per-window supply (edit it there or here — they are linked). See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
         </is>
@@ -1438,10 +1522,10 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C16:K16"/>
     <mergeCell ref="C5:K5"/>
+    <mergeCell ref="B26:K26"/>
     <mergeCell ref="C2:G2"/>
-    <mergeCell ref="B24:K24"/>
     <mergeCell ref="C12:K12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1588,6 +1672,26 @@
       <c r="C6" s="38" t="n">
         <v>0.95</v>
       </c>
+      <c r="R6" s="35">
+        <f>'Competitive Analysis'!C14</f>
+        <v/>
+      </c>
+      <c r="S6" s="36">
+        <f>'Competitive Analysis'!D14</f>
+        <v/>
+      </c>
+      <c r="T6" s="37">
+        <f>'Competitive Analysis'!E14</f>
+        <v/>
+      </c>
+      <c r="V6">
+        <f>IFERROR(VALUE(RIGHT(T6,4))*4+MATCH(LEFT(T6,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W6">
+        <f>IF(V6="","",IF(V6&lt;=$Z$1,0,MAX(1,INT((V6-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="14.4" customHeight="1">
       <c r="B7" s="30" t="inlineStr">
@@ -1600,11 +1704,6 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="R7" s="29" t="inlineStr">
-        <is>
-          <t>PROPOSED PIPELINE (scenario toggle)</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="14.4" customHeight="1">
       <c r="B8" s="30" t="inlineStr">
@@ -1615,24 +1714,9 @@
       <c r="C8" s="39" t="n">
         <v>150</v>
       </c>
-      <c r="R8" s="33" t="inlineStr">
-        <is>
-          <t>Property</t>
-        </is>
-      </c>
-      <c r="S8" s="33" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="T8" s="33" t="inlineStr">
-        <is>
-          <t>Est. Delivery</t>
-        </is>
-      </c>
-      <c r="U8" s="33" t="inlineStr">
-        <is>
-          <t>Built In</t>
+      <c r="R8" s="29" t="inlineStr">
+        <is>
+          <t>PROPOSED PIPELINE (scenario toggle)</t>
         </is>
       </c>
     </row>
@@ -1645,31 +1729,25 @@
       <c r="C9" s="39" t="n">
         <v>300</v>
       </c>
-      <c r="R9" s="35" t="inlineStr">
-        <is>
-          <t>Vista Point</t>
-        </is>
-      </c>
-      <c r="S9" s="36" t="n">
-        <v>892</v>
-      </c>
-      <c r="T9" s="40" t="inlineStr"/>
-      <c r="U9" s="40" t="inlineStr">
-        <is>
-          <t>Bear only</t>
-        </is>
-      </c>
-      <c r="V9">
-        <f>IFERROR(VALUE(RIGHT(T9,4))*4+MATCH(LEFT(T9,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W9">
-        <f>IF(V9="","",IF(V9&lt;=$Z$1,0,MAX(1,INT((V9-$Z$2)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>IF(U9="All",1,IF(U9="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U9="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
-        <v/>
+      <c r="R9" s="33" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="S9" s="33" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="T9" s="33" t="inlineStr">
+        <is>
+          <t>Est. Delivery</t>
+        </is>
+      </c>
+      <c r="U9" s="33" t="inlineStr">
+        <is>
+          <t>Built In</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="14.4" customHeight="1">
@@ -1688,17 +1766,13 @@
       </c>
       <c r="R10" s="35" t="inlineStr">
         <is>
-          <t>Seasons on the Bench</t>
+          <t>Vista Point</t>
         </is>
       </c>
       <c r="S10" s="36" t="n">
-        <v>300</v>
-      </c>
-      <c r="T10" s="40" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
+        <v>892</v>
+      </c>
+      <c r="T10" s="40" t="inlineStr"/>
       <c r="U10" s="40" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -1729,13 +1803,17 @@
       </c>
       <c r="R11" s="35" t="inlineStr">
         <is>
-          <t>1519 South Londoner Avenue</t>
+          <t>Seasons on the Bench</t>
         </is>
       </c>
       <c r="S11" s="36" t="n">
-        <v>189</v>
-      </c>
-      <c r="T11" s="40" t="inlineStr"/>
+        <v>300</v>
+      </c>
+      <c r="T11" s="40" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
       <c r="U11" s="40" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -1757,11 +1835,11 @@
     <row r="12" ht="14.4" customHeight="1">
       <c r="R12" s="35" t="inlineStr">
         <is>
-          <t>3300 South Vista Avenue</t>
+          <t>Kootenai &amp; Federal Way (Hawkins)</t>
         </is>
       </c>
       <c r="S12" s="36" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="T12" s="40" t="inlineStr"/>
       <c r="U12" s="40" t="inlineStr">
@@ -1785,17 +1863,13 @@
     <row r="13" ht="14.4" customHeight="1">
       <c r="R13" s="35" t="inlineStr">
         <is>
-          <t>The Ranahan</t>
+          <t>1519 South Londoner Avenue</t>
         </is>
       </c>
       <c r="S13" s="36" t="n">
-        <v>138</v>
-      </c>
-      <c r="T13" s="40" t="inlineStr">
-        <is>
-          <t>Q4 2028</t>
-        </is>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="T13" s="40" t="inlineStr"/>
       <c r="U13" s="40" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -1817,11 +1891,11 @@
     <row r="14" ht="14.4" customHeight="1">
       <c r="R14" s="35" t="inlineStr">
         <is>
-          <t>Station Village</t>
+          <t>3300 South Vista Avenue</t>
         </is>
       </c>
       <c r="S14" s="36" t="n">
-        <v>86</v>
+        <v>183</v>
       </c>
       <c r="T14" s="40" t="inlineStr"/>
       <c r="U14" s="40" t="inlineStr">
@@ -1842,8 +1916,66 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="14.4" customHeight="1"/>
-    <row r="16" ht="14.4" customHeight="1"/>
+    <row r="15" ht="14.4" customHeight="1">
+      <c r="R15" s="35" t="inlineStr">
+        <is>
+          <t>The Ranahan</t>
+        </is>
+      </c>
+      <c r="S15" s="36" t="n">
+        <v>138</v>
+      </c>
+      <c r="T15" s="40" t="inlineStr">
+        <is>
+          <t>Q4 2028</t>
+        </is>
+      </c>
+      <c r="U15" s="40" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V15">
+        <f>IFERROR(VALUE(RIGHT(T15,4))*4+MATCH(LEFT(T15,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W15">
+        <f>IF(V15="","",IF(V15&lt;=$Z$1,0,MAX(1,INT((V15-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>IF(U15="All",1,IF(U15="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U15="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="14.4" customHeight="1">
+      <c r="R16" s="35" t="inlineStr">
+        <is>
+          <t>Station Village</t>
+        </is>
+      </c>
+      <c r="S16" s="36" t="n">
+        <v>86</v>
+      </c>
+      <c r="T16" s="40" t="inlineStr"/>
+      <c r="U16" s="40" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V16">
+        <f>IFERROR(VALUE(RIGHT(T16,4))*4+MATCH(LEFT(T16,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W16">
+        <f>IF(V16="","",IF(V16&lt;=$Z$1,0,MAX(1,INT((V16-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>IF(U16="All",1,IF(U16="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U16="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
     <row r="17" ht="14.4" customHeight="1">
       <c r="B17" s="30" t="inlineStr">
         <is>
@@ -2002,31 +2134,31 @@
         <v>334</v>
       </c>
       <c r="I19" s="44">
-        <f>SUMIFS('Competitive Analysis'!$D$5:$D$21,'Competitive Analysis'!$M$5:$M$21,"&gt;="&amp;8102,'Competitive Analysis'!$M$5:$M$21,"&lt;="&amp;8105)</f>
+        <f>SUMIFS('Competitive Analysis'!$D$5:$D$23,'Competitive Analysis'!$M$5:$M$23,"&gt;="&amp;8102,'Competitive Analysis'!$M$5:$M$23,"&lt;="&amp;8105)</f>
         <v/>
       </c>
       <c r="J19" s="45">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,1)+SUMIFS($S$9:$S$14,$W$9:$W$14,1,$X$9:$X$14,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,1)+SUMIFS($S$10:$S$16,$W$10:$W$16,1,$X$10:$X$16,1)</f>
         <v/>
       </c>
       <c r="K19" s="45">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,2)+SUMIFS($S$9:$S$14,$W$9:$W$14,2,$X$9:$X$14,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,2)+SUMIFS($S$10:$S$16,$W$10:$W$16,2,$X$10:$X$16,1)</f>
         <v/>
       </c>
       <c r="L19" s="45">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,3)+SUMIFS($S$9:$S$14,$W$9:$W$14,3,$X$9:$X$14,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,3)+SUMIFS($S$10:$S$16,$W$10:$W$16,3,$X$10:$X$16,1)</f>
         <v/>
       </c>
       <c r="M19" s="45">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,4)+SUMIFS($S$9:$S$14,$W$9:$W$14,4,$X$9:$X$14,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,4)+SUMIFS($S$10:$S$16,$W$10:$W$16,4,$X$10:$X$16,1)</f>
         <v/>
       </c>
       <c r="N19" s="45">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,5)+SUMIFS($S$9:$S$14,$W$9:$W$14,5,$X$9:$X$14,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,5)+SUMIFS($S$10:$S$16,$W$10:$W$16,5,$X$10:$X$16,1)</f>
         <v/>
       </c>
       <c r="O19" s="45">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,6)+SUMIFS($S$9:$S$14,$W$9:$W$14,6,$X$9:$X$14,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,6)+SUMIFS($S$10:$S$16,$W$10:$W$16,6,$X$10:$X$16,1)</f>
         <v/>
       </c>
     </row>
@@ -3404,7 +3536,7 @@
       </c>
       <c r="E68" s="71" t="inlineStr">
         <is>
-          <t>30 / 27</t>
+          <t>62 / 27</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3599,7 @@
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Bear,Base,Bull"</formula1>
     </dataValidation>
-    <dataValidation sqref="U9 U10 U11 U12 U13 U14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U10 U11 U12 U13 U14 U15 U16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Bear only,Bear+Base,All,None"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3481,7 +3613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3912,28 +4044,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>The Ranahan</t>
+          <t>The Quarter at Harris Ranch</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4227 E Brightside St</t>
+          <t>3430-3450 S Hopes Well Way, Boise 83716</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>138</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2027</v>
+        <v>32</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q1 2027</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
       <c r="H8" s="72" t="n"/>
@@ -3945,32 +4074,35 @@
       <c r="N8" s="73" t="n"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>Diligence</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: under construction</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Seasons on the Bench</t>
+          <t>The Ranahan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2521 W Victory Rd</t>
+          <t>4227 E Brightside St</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>300</v>
+        <v>138</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2027</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Q3 2028</t>
+          <t>Q4 2028</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3987,28 +4119,33 @@
       <c r="N9" s="73" t="n"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>RealPage</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3300 South Vista Avenue</t>
+          <t>Seasons on the Bench</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3300 S Vista Ave</t>
+          <t>2521 W Victory Rd</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>300</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -4036,16 +4173,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1519 South Londoner Avenue</t>
+          <t>3300 South Vista Avenue</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1519 S Londoner Ave</t>
+          <t>3300 S Vista Ave</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -4073,16 +4210,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Station Village</t>
+          <t>1519 South Londoner Avenue</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2350 W Kootenai St</t>
+          <t>1519 S Londoner Ave</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -4110,16 +4247,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vista Point</t>
+          <t>Station Village</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2017 W Victory Rd</t>
+          <t>2350 W Kootenai St</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>892</v>
+        <v>86</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -4141,6 +4278,80 @@
       <c r="P13" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Vista Point</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2017 W Victory Rd</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>892</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="H14" s="72" t="n"/>
+      <c r="I14" s="72" t="n"/>
+      <c r="J14" s="72" t="n"/>
+      <c r="K14" s="73" t="n"/>
+      <c r="L14" s="73" t="n"/>
+      <c r="M14" s="73" t="n"/>
+      <c r="N14" s="73" t="n"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>RealPage</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Kootenai &amp; Federal Way (Hawkins)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kootenai St &amp; S Federal Way, Boise 83705</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>194</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="H15" s="72" t="n"/>
+      <c r="I15" s="72" t="n"/>
+      <c r="J15" s="72" t="n"/>
+      <c r="K15" s="73" t="n"/>
+      <c r="L15" s="73" t="n"/>
+      <c r="M15" s="73" t="n"/>
+      <c r="N15" s="73" t="n"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Diligence</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H17"/>
+  <dimension ref="B2:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -4448,117 +4659,279 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>The Quarter at Harris Ranch</t>
+        </is>
+      </c>
+      <c r="C12" s="75" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D12" s="75" t="inlineStr">
+        <is>
+          <t>Q1 2027</t>
+        </is>
+      </c>
+      <c r="E12" s="35" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="35" t="inlineStr">
+        <is>
+          <t>AUDIT FIND (July 2026): permit-log-only project — NO CoStar, RealPage, or press footprint. Barber Valley Development / Dave Evans Construction at 3430-3450 S Hopes Well Way (~2.5 mi): grading permit GRD24-00089 (Feb 2025) for 'new multi-family buildings'; Building C permit BLD25-00272 ISSUED 9/10/2025 ($13.3M, 4-story, 32 units, podium garage, pool/spa). Multi-building site — 32u is Bldg C only; total unverified (pull DRH24-00233 to size). Likely the first rental phase of the Harris Ranch Town Center blocks.</t>
+        </is>
+      </c>
+      <c r="H12" s="35" t="inlineStr">
+        <is>
+          <t>https://www.djc.com/stories/images/permits/CityofBoise0901-0930.pdf</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="B13" s="74" t="inlineStr">
-        <is>
-          <t>SHADOW SUPPLY (latent / untracked — watch list)</t>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>Kootenai &amp; Federal Way (Hawkins)</t>
+        </is>
+      </c>
+      <c r="C13" s="75" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D13" s="75" t="n"/>
+      <c r="E13" s="35" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F13" s="35" t="n"/>
+      <c r="G13" s="35" t="inlineStr">
+        <is>
+          <t>AUDIT FIND: Hawkins Companies (same sponsor as The Judy) — 194 units, 5-story + 2k sf retail + 323 stalls on the triangular Bench lot at Kootenai St &amp; S Federal Way (~4.1 mi). Council approved Feb 2025 (appeal denied); updated design submitted ~Oct 2025; Hawkins said construction 'possibly within a year' (Aug 2025). No building permit through June 2026. Not in CoStar/RealPage.</t>
+        </is>
+      </c>
+      <c r="H13" s="35" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2025/02/06/black-cliffs-appeal/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="42" t="inlineStr">
-        <is>
-          <t>Property / Site</t>
-        </is>
-      </c>
-      <c r="C14" s="42" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="D14" s="42" t="inlineStr">
-        <is>
-          <t>Est. Delivery</t>
-        </is>
-      </c>
-      <c r="E14" s="42" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F14" s="42" t="inlineStr">
-        <is>
-          <t>Leasing Pace</t>
-        </is>
-      </c>
-      <c r="G14" s="42" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="H14" s="42" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>10 S Latah St</t>
+        </is>
+      </c>
+      <c r="C14" s="75" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D14" s="75" t="n"/>
+      <c r="E14" s="35" t="inlineStr">
+        <is>
+          <t>exclude - beyond 5-mi radius (~5.6 mi)</t>
+        </is>
+      </c>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="35" t="inlineStr">
+        <is>
+          <t>AUDIT (documented, outside ring): EMW 10 Latah LLC 4-story mixed-use, 41 units + ground-floor retail at Latah/Alpine on the Bench; building permit ISSUED 5/20/2026 ($10.2M). Real UC supply but outside the 5-mile radius — belongs to the same adjacent-submarket cluster as LOCAL Boise/Armory.</t>
+        </is>
+      </c>
+      <c r="H14" s="35" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2025/04/09/10-s-latah-boise/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Barber Valley SP-02 HDR block (Parkcenter)</t>
-        </is>
-      </c>
-      <c r="C15" s="75" t="n"/>
+          <t>Capitol Campus / Lusk District</t>
+        </is>
+      </c>
+      <c r="C15" s="75" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
       <c r="D15" s="75" t="n"/>
-      <c r="E15" s="35" t="n"/>
+      <c r="E15" s="35" t="inlineStr">
+        <is>
+          <t>exclude - beyond 5-mi radius (~5.4 mi)</t>
+        </is>
+      </c>
       <c r="F15" s="35" t="n"/>
       <c r="G15" s="35" t="inlineStr">
         <is>
-          <t>Land-use analysis site CR-51: 11.5 ac zoned SP-02 with High-Density Residential FLU inside the adopted Barber Valley Specific Plan; OUTSIDE the Airport Influence Area. Entitled/planned multifamily block, master-developed by Barber Valley Development (Harris Family LP); HDR blocks typically sold to merchant apartment developers. No active application found — the most apartment-competitive latent site in the 5-mi ring.</t>
+          <t>AUDIT (documented, outside ring): J. Fisher + City of Boise + CCDC affordable redevelopment near BSU, 325+ income-restricted units, groundbreak targeted Fall 2026 (BSU exited the partnership Feb 2026 but the city block proceeds). Outside the 5-mile radius; classic vendor-invisible affordable pipeline — watch for spillover effects.</t>
         </is>
       </c>
       <c r="H15" s="35" t="inlineStr">
         <is>
+          <t>https://www.cityofboise.org/programs/housing/capitol-campus/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="74" t="inlineStr">
+        <is>
+          <t>SHADOW SUPPLY (latent / untracked — watch list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="42" t="inlineStr">
+        <is>
+          <t>Property / Site</t>
+        </is>
+      </c>
+      <c r="C18" s="42" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="inlineStr">
+        <is>
+          <t>Est. Delivery</t>
+        </is>
+      </c>
+      <c r="E18" s="42" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F18" s="42" t="inlineStr">
+        <is>
+          <t>Leasing Pace</t>
+        </is>
+      </c>
+      <c r="G18" s="42" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="H18" s="42" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>Barber Valley SP-02 HDR block (Parkcenter)</t>
+        </is>
+      </c>
+      <c r="C19" s="75" t="n"/>
+      <c r="D19" s="75" t="n"/>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="35" t="n"/>
+      <c r="G19" s="35" t="inlineStr">
+        <is>
+          <t>Land-use analysis site CR-51: 11.5 ac zoned SP-02 with High-Density Residential FLU inside the adopted Barber Valley Specific Plan; OUTSIDE the Airport Influence Area. Entitled/planned multifamily block, master-developed by Barber Valley Development (Harris Family LP); HDR blocks typically sold to merchant apartment developers. No active application found — the most apartment-competitive latent site in the 5-mi ring. UPDATE (audit, July 2026): Harris Ranch Town Center plan refreshed June 2026 (specialty market, restaurants, hotel, ~100 for-sale homes, 250-400 planned apartments between Warm Springs &amp; ParkCenter) — and its first rental phase appears to be THE QUARTER at Harris Ranch, now under construction and tracked in the chart. Dedupe: this shadow row covers the remaining unbuilt HDR capacity only.</t>
+        </is>
+      </c>
+      <c r="H19" s="35" t="inlineStr">
+        <is>
           <t>https://boisedev.com/news/2021/11/12/harris-ranch-town-center/</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="35" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>McDonald Tract (S Oakland Ave)</t>
         </is>
       </c>
-      <c r="C16" s="75" t="n"/>
-      <c r="D16" s="75" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="35" t="n"/>
-      <c r="G16" s="35" t="inlineStr">
+      <c r="C20" s="75" t="n"/>
+      <c r="D20" s="75" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="35" t="n"/>
+      <c r="G20" s="35" t="inlineStr">
         <is>
           <t>Land-use analysis site CR-57: 10.3 ac zoned R-3 (multifamily by-right) with Mixed Use FLU, outside the Airport Influence Area. Dormant — no application, listing, or news found; owner not published. By-right MF capacity makes it a genuine watch item despite no activity.</t>
         </is>
       </c>
-      <c r="H16" s="35" t="inlineStr">
+      <c r="H20" s="35" t="inlineStr">
         <is>
           <t>https://www.redfin.com/ID/Boise/1507-S-Oakland-Ave-83706/home/109555986</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="35" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>East Columbia bench (Rush Valley / planned community)</t>
         </is>
       </c>
-      <c r="C17" s="75" t="n"/>
-      <c r="D17" s="75" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="35" t="inlineStr">
+      <c r="C21" s="75" t="n"/>
+      <c r="D21" s="75" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="35" t="inlineStr">
         <is>
           <t>Land-use analysis sites CR-2/CR-3/CR-5: ~1,700+ ac far-SE 'East Columbia' bench with Boise 'Planned Community' FLU — one of three strategic planning areas the city began studying Jan 2026. Rush Valley subdivision portion (Conger Group/DevCo) approved but capped and largely unbuilt; residential blocked by missing secondary fire access and landowner coordination (Simplot, Micron, Ball Ventures, Murgoitio). Long-horizon supply, not near-term.</t>
         </is>
       </c>
-      <c r="H17" s="35" t="inlineStr">
+      <c r="H21" s="35" t="inlineStr">
         <is>
           <t>https://boisedev.com/news/2026/01/28/southeast-boise-planning/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>East Hollow (CBH, south of Micron)</t>
+        </is>
+      </c>
+      <c r="C22" s="75" t="n"/>
+      <c r="D22" s="75" t="n"/>
+      <c r="E22" s="35" t="n"/>
+      <c r="F22" s="35" t="n"/>
+      <c r="G22" s="35" t="inlineStr">
+        <is>
+          <t>AUDIT WATCH: CBH Homes pre-application (Ada County, Nov 2025) for ~1,200 ac / ~7,000 homes (apartments + SF mix) south of Micron near I-84/Eisenman and the future Lake Hazel extension — at/just outside the ring's SE edge, 2029+ horizon. Distinct from East Columbia/Rush Valley. Long-dated but material to the airport/Micron corridor.</t>
+        </is>
+      </c>
+      <c r="H22" s="35" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2025/11/26/east-hollow-7000/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>Arbor Village at Hillcrest conversion (verify)</t>
+        </is>
+      </c>
+      <c r="C23" s="75" t="n"/>
+      <c r="D23" s="75" t="n"/>
+      <c r="E23" s="35" t="n"/>
+      <c r="F23" s="35" t="n"/>
+      <c r="G23" s="35" t="inlineStr">
+        <is>
+          <t>AUDIT WATCH: 2022 proposal to convert a 115-room assisted-living building to up to 77 market apartments in the Hillcrest area (83705, near the scored W Hillcrest Ln parcel); no update found — unverified. Conversions add rental supply without appearing in any construction pipeline.</t>
+        </is>
+      </c>
+      <c r="H23" s="35" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2022/02/10/arbor-village-hillcrest/</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B13:H13"/>
     <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CanyonRidge/supply/Canyon_Ridge__Supply_Chart.xlsx
+++ b/CanyonRidge/supply/Canyon_Ridge__Supply_Chart.xlsx
@@ -777,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M26"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -864,7 +864,7 @@
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>STABILIZED / STABILIZING (5 properties, 492 units)</t>
+          <t>STABILIZED / STABILIZING (6 properties, 779 units)</t>
         </is>
       </c>
     </row>
@@ -1012,11 +1012,11 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Mesa Pointe Apartments</t>
+          <t>★ Canyon Ridge  (SUBJECT)</t>
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>12</v>
+        <v>287</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
@@ -1024,25 +1024,29 @@
         </is>
       </c>
       <c r="F9" s="9" t="n">
-        <v>1</v>
+        <v>0.979094</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>1647</v>
+        <v>2271.013010540184</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Rre Mesa Pointe Llc</t>
+          <t>Hawkins Companies</t>
         </is>
       </c>
       <c r="I9" s="11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Low-Rise</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n"/>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Year built: 2024/2025; SUBJECT — this deal</t>
+        </is>
+      </c>
       <c r="M9">
         <f>IFERROR(VALUE(RIGHT(E9,4))*4+MATCH(LEFT(E9,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
@@ -1054,30 +1058,30 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Veazey Apartments</t>
+          <t>Mesa Pointe Apartments</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Q4 2024</t>
+          <t>Q3 2024</t>
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>0.971429</v>
+        <v>1</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>1547</v>
+        <v>1647</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Conrad J Frank</t>
+          <t>Rre Mesa Pointe Llc</t>
         </is>
       </c>
       <c r="I10" s="11" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
@@ -1090,54 +1094,54 @@
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="13" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Veazey Apartments</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Q4 2024</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>0.971429</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>1547</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Conrad J Frank</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Low-Rise</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="n"/>
+      <c r="M11">
+        <f>IFERROR(VALUE(RIGHT(E11,4))*4+MATCH(LEFT(E11,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>UNDER CONSTRUCTION (2 properties, 62 units)</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>The Quarter at Harris Ranch</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Q1 2027</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="n"/>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J13" s="14" t="n"/>
-      <c r="K13" s="15" t="inlineStr">
-        <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: under construction</t>
-        </is>
-      </c>
-      <c r="M13">
-        <f>IFERROR(VALUE(RIGHT(E13,4))*4+MATCH(LEFT(E13,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -1146,15 +1150,15 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>737 ParkCenter</t>
+          <t>The Quarter at Harris Ranch</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Q3 2027</t>
+          <t>Q1 2027</t>
         </is>
       </c>
       <c r="F14" s="17" t="n"/>
@@ -1165,20 +1169,16 @@
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>Scott G Kimball</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I14" s="19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J14" s="14" t="inlineStr">
-        <is>
-          <t>Low-Rise</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="J14" s="14" t="n"/>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>Diligence: under construction</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: under construction</t>
         </is>
       </c>
       <c r="M14">
@@ -1186,58 +1186,58 @@
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="21" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>737 ParkCenter</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Q3 2027</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>Scott G Kimball</t>
+        </is>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Low-Rise</t>
+        </is>
+      </c>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t>Diligence: under construction</t>
+        </is>
+      </c>
+      <c r="M15">
+        <f>IFERROR(VALUE(RIGHT(E15,4))*4+MATCH(LEFT(E15,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>PROPOSED (7 properties, 1,982 units)</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>Seasons on the Bench</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="n">
-        <v>300</v>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="F17" s="25" t="n"/>
-      <c r="G17" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" s="27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J17" s="22" t="inlineStr">
-        <is>
-          <t>Garden</t>
-        </is>
-      </c>
-      <c r="K17" s="23" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
-        </is>
-      </c>
-      <c r="M17">
-        <f>IFERROR(VALUE(RIGHT(E17,4))*4+MATCH(LEFT(E17,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
       </c>
     </row>
     <row r="18">
@@ -1246,15 +1246,15 @@
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>The Ranahan</t>
+          <t>Seasons on the Bench</t>
         </is>
       </c>
       <c r="D18" s="24" t="n">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q3 2028</t>
         </is>
       </c>
       <c r="F18" s="25" t="n"/>
@@ -1265,20 +1265,20 @@
       </c>
       <c r="H18" s="23" t="inlineStr">
         <is>
-          <t>Dave Evans Construction</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I18" s="27" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J18" s="22" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M18">
@@ -1292,15 +1292,15 @@
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>Vista Point</t>
+          <t>The Ranahan</t>
         </is>
       </c>
       <c r="D19" s="24" t="n">
-        <v>892</v>
+        <v>138</v>
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q4 2028</t>
         </is>
       </c>
       <c r="F19" s="25" t="n"/>
@@ -1311,11 +1311,11 @@
       </c>
       <c r="H19" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Dave Evans Construction</t>
         </is>
       </c>
       <c r="I19" s="27" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J19" s="22" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="K19" s="23" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
       <c r="M19">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>Kootenai &amp; Federal Way (Hawkins)</t>
+          <t>Vista Point</t>
         </is>
       </c>
       <c r="D20" s="24" t="n">
-        <v>194</v>
+        <v>892</v>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
@@ -1361,12 +1361,16 @@
         </is>
       </c>
       <c r="I20" s="27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J20" s="22" t="n"/>
+        <v>3.4</v>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
       <c r="K20" s="23" t="inlineStr">
         <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M20">
@@ -1380,11 +1384,11 @@
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>1519 South Londoner Avenue</t>
+          <t>Kootenai &amp; Federal Way (Hawkins)</t>
         </is>
       </c>
       <c r="D21" s="24" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
@@ -1403,16 +1407,12 @@
         </is>
       </c>
       <c r="I21" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" s="22" t="inlineStr">
-        <is>
-          <t>Garden</t>
-        </is>
-      </c>
+        <v>4.1</v>
+      </c>
+      <c r="J21" s="22" t="n"/>
       <c r="K21" s="23" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
         </is>
       </c>
       <c r="M21">
@@ -1426,11 +1426,11 @@
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>3300 South Vista Avenue</t>
+          <t>1519 South Londoner Avenue</t>
         </is>
       </c>
       <c r="D22" s="24" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
@@ -1449,11 +1449,11 @@
         </is>
       </c>
       <c r="I22" s="27" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J22" s="22" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr">
@@ -1472,11 +1472,11 @@
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>Station Village</t>
+          <t>3300 South Vista Avenue</t>
         </is>
       </c>
       <c r="D23" s="24" t="n">
-        <v>86</v>
+        <v>183</v>
       </c>
       <c r="E23" s="22" t="inlineStr">
         <is>
@@ -1491,15 +1491,15 @@
       </c>
       <c r="H23" s="23" t="inlineStr">
         <is>
-          <t>Privately Owned</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I23" s="27" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="J23" s="22" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K23" s="23" t="inlineStr">
@@ -1512,8 +1512,54 @@
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="28" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>Station Village</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="n">
+        <v>86</v>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F24" s="25" t="n"/>
+      <c r="G24" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>Privately Owned</t>
+        </is>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+        </is>
+      </c>
+      <c r="M24">
+        <f>IFERROR(VALUE(RIGHT(E24,4))*4+MATCH(LEFT(E24,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>* 5-Mile radius. Rent ($) = HelloData mix-weighted asking where covered, else market asking (CoStar). Proximity (mi) = straight-line distance from the subject. Est. Delivery drives the Supply &amp; Absorption tab's per-window supply (edit it there or here — they are linked). See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
         </is>
@@ -1522,11 +1568,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="C16:K16"/>
     <mergeCell ref="C5:K5"/>
-    <mergeCell ref="B26:K26"/>
     <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="B27:K27"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C17:K17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1643,15 +1689,15 @@
         </is>
       </c>
       <c r="R5" s="35">
-        <f>'Competitive Analysis'!C13</f>
+        <f>'Competitive Analysis'!C14</f>
         <v/>
       </c>
       <c r="S5" s="36">
-        <f>'Competitive Analysis'!D13</f>
+        <f>'Competitive Analysis'!D14</f>
         <v/>
       </c>
       <c r="T5" s="37">
-        <f>'Competitive Analysis'!E13</f>
+        <f>'Competitive Analysis'!E14</f>
         <v/>
       </c>
       <c r="V5">
@@ -1673,15 +1719,15 @@
         <v>0.95</v>
       </c>
       <c r="R6" s="35">
-        <f>'Competitive Analysis'!C14</f>
+        <f>'Competitive Analysis'!C15</f>
         <v/>
       </c>
       <c r="S6" s="36">
-        <f>'Competitive Analysis'!D14</f>
+        <f>'Competitive Analysis'!D15</f>
         <v/>
       </c>
       <c r="T6" s="37">
-        <f>'Competitive Analysis'!E14</f>
+        <f>'Competitive Analysis'!E15</f>
         <v/>
       </c>
       <c r="V6">
@@ -2134,7 +2180,7 @@
         <v>334</v>
       </c>
       <c r="I19" s="44">
-        <f>SUMIFS('Competitive Analysis'!$D$5:$D$23,'Competitive Analysis'!$M$5:$M$23,"&gt;="&amp;8102,'Competitive Analysis'!$M$5:$M$23,"&lt;="&amp;8105)</f>
+        <f>SUMIFS('Competitive Analysis'!$D$5:$D$24,'Competitive Analysis'!$M$5:$M$24,"&gt;="&amp;8102,'Competitive Analysis'!$M$5:$M$24,"&lt;="&amp;8105)</f>
         <v/>
       </c>
       <c r="J19" s="45">
@@ -2277,24 +2323,14 @@
     <row r="23" ht="14.4" customHeight="1">
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Market Rent  (CoStar→HD)</t>
-        </is>
-      </c>
-      <c r="C23" s="48" t="n">
-        <v>1811</v>
-      </c>
-      <c r="D23" s="48" t="n">
-        <v>1845</v>
-      </c>
-      <c r="E23" s="48" t="n">
-        <v>1885</v>
-      </c>
-      <c r="F23" s="48" t="n">
-        <v>1925</v>
-      </c>
-      <c r="G23" s="48" t="n">
-        <v>1953</v>
-      </c>
+          <t xml:space="preserve">  Market Rent  (HelloData mix-wtd)</t>
+        </is>
+      </c>
+      <c r="C23" s="48" t="n"/>
+      <c r="D23" s="48" t="n"/>
+      <c r="E23" s="48" t="n"/>
+      <c r="F23" s="48" t="n"/>
+      <c r="G23" s="48" t="n"/>
       <c r="H23" s="48" t="n">
         <v>1944</v>
       </c>
@@ -2389,21 +2425,11 @@
           <t xml:space="preserve">  Effective Rent</t>
         </is>
       </c>
-      <c r="C25" s="48" t="n">
-        <v>1793</v>
-      </c>
-      <c r="D25" s="48" t="n">
-        <v>1832</v>
-      </c>
-      <c r="E25" s="48" t="n">
-        <v>1867</v>
-      </c>
-      <c r="F25" s="48" t="n">
-        <v>1897</v>
-      </c>
-      <c r="G25" s="48" t="n">
-        <v>1953</v>
-      </c>
+      <c r="C25" s="48" t="n"/>
+      <c r="D25" s="48" t="n"/>
+      <c r="E25" s="48" t="n"/>
+      <c r="F25" s="48" t="n"/>
+      <c r="G25" s="48" t="n"/>
       <c r="H25" s="48" t="n">
         <v>1795</v>
       </c>
@@ -3452,7 +3478,7 @@
       </c>
       <c r="E61" s="71" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3490,7 @@
       </c>
       <c r="E62" s="71" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3502,7 @@
       </c>
       <c r="E63" s="71" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3514,7 @@
       </c>
       <c r="E64" s="71" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3526,7 @@
       </c>
       <c r="E65" s="71" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3597,7 @@
     <row r="73" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
       <c r="B73" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">    -Y1: roster (CoStar-tracked) 47 + subj 287 vs CoStar 334   (tie ✓)</t>
+          <t xml:space="preserve">    -Y1: roster (CoStar-tracked) 334 vs CoStar 334   (tie ✓)</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3769,16 +3795,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mesa Pointe Apartments</t>
+          <t>Canyon Ridge</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1805 W Overland Rd</t>
+          <t>2552 E Gowen Rd</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>287</v>
       </c>
       <c r="D3" t="n">
         <v>2024</v>
@@ -3798,42 +3824,56 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="H3" s="72" t="n"/>
-      <c r="I3" s="72" t="n"/>
+      <c r="H3" s="72" t="n">
+        <v>0.979094</v>
+      </c>
+      <c r="I3" s="72" t="n">
+        <v>0.993</v>
+      </c>
       <c r="J3" s="72" t="n"/>
       <c r="K3" s="73" t="n">
-        <v>1647</v>
-      </c>
-      <c r="L3" s="73" t="n"/>
-      <c r="M3" s="73" t="n"/>
-      <c r="N3" s="73" t="n"/>
+        <v>2332</v>
+      </c>
+      <c r="L3" s="73" t="n">
+        <v>2223</v>
+      </c>
+      <c r="M3" s="73" t="n">
+        <v>2271.013010540184</v>
+      </c>
+      <c r="N3" s="73" t="n">
+        <v>2271.013010540184</v>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>CoStar</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
+          <t>CoStar+RealPage</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Year built: 2024/2025; SUBJECT — this deal</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>The Mill at Loggers Creek</t>
+          <t>Mesa Pointe Apartments</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1250 S Division Ave</t>
+          <t>1805 W Overland Rd</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>2024</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Q2 2024</t>
+          <t>Q3 2024</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3846,56 +3886,42 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="H4" s="72" t="n">
-        <v>0.912</v>
-      </c>
-      <c r="I4" s="72" t="n">
-        <v>0.9360000000000001</v>
-      </c>
+      <c r="H4" s="72" t="n"/>
+      <c r="I4" s="72" t="n"/>
       <c r="J4" s="72" t="n"/>
       <c r="K4" s="73" t="n">
-        <v>2096</v>
-      </c>
-      <c r="L4" s="73" t="n">
-        <v>2150</v>
-      </c>
-      <c r="M4" s="73" t="n">
-        <v>2148.791666666667</v>
-      </c>
-      <c r="N4" s="73" t="n">
-        <v>2129.791666666667</v>
-      </c>
+        <v>1647</v>
+      </c>
+      <c r="L4" s="73" t="n"/>
+      <c r="M4" s="73" t="n"/>
+      <c r="N4" s="73" t="n"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Occ: CoStar 91% vs RealPage 94%</t>
-        </is>
-      </c>
+          <t>CoStar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>The Betty</t>
+          <t>The Mill at Loggers Creek</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2550 W Targee St</t>
+          <t>1250 S Division Ave</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c r="D5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Q4 2023</t>
+          <t>Q2 2024</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3909,20 +3935,24 @@
         </is>
       </c>
       <c r="H5" s="72" t="n">
-        <v>0.934783</v>
+        <v>0.912</v>
       </c>
       <c r="I5" s="72" t="n">
-        <v>0.961</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="J5" s="72" t="n"/>
       <c r="K5" s="73" t="n">
-        <v>1577</v>
+        <v>2096</v>
       </c>
       <c r="L5" s="73" t="n">
-        <v>1273</v>
-      </c>
-      <c r="M5" s="73" t="n"/>
-      <c r="N5" s="73" t="n"/>
+        <v>2150</v>
+      </c>
+      <c r="M5" s="73" t="n">
+        <v>2148.791666666667</v>
+      </c>
+      <c r="N5" s="73" t="n">
+        <v>2129.791666666667</v>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -3930,30 +3960,30 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Occ: CoStar 93% vs RealPage 96%; Rent: CoStar ask $1,577 vs RealPage eff $1,273</t>
+          <t>Occ: CoStar 91% vs RealPage 94%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>The Timbers at Harris Ranch</t>
+          <t>The Betty</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3469 S Old Hickory Way</t>
+          <t>2550 W Targee St</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>274</v>
+        <v>46</v>
       </c>
       <c r="D6" t="n">
         <v>2023</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Q2 2023</t>
+          <t>Q4 2023</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3967,24 +3997,20 @@
         </is>
       </c>
       <c r="H6" s="72" t="n">
-        <v>0.974453</v>
+        <v>0.934783</v>
       </c>
       <c r="I6" s="72" t="n">
-        <v>0.996</v>
+        <v>0.961</v>
       </c>
       <c r="J6" s="72" t="n"/>
       <c r="K6" s="73" t="n">
-        <v>2213</v>
+        <v>1577</v>
       </c>
       <c r="L6" s="73" t="n">
-        <v>2303</v>
-      </c>
-      <c r="M6" s="73" t="n">
-        <v>2147.615759341101</v>
-      </c>
-      <c r="N6" s="73" t="n">
-        <v>2147.615759341101</v>
-      </c>
+        <v>1273</v>
+      </c>
+      <c r="M6" s="73" t="n"/>
+      <c r="N6" s="73" t="n"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -3992,72 +4018,92 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Year built: 2023/2024; Occ: CoStar 97% vs RealPage 100%</t>
+          <t>Occ: CoStar 93% vs RealPage 96%; Rent: CoStar ask $1,577 vs RealPage eff $1,273</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>737 ParkCenter</t>
+          <t>The Timbers at Harris Ranch</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>787 E Parkcenter Blvd</t>
+          <t>3469 S Old Hickory Way</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
+        <v>274</v>
       </c>
       <c r="D7" t="n">
-        <v>2027</v>
+        <v>2023</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Q3 2027</t>
+          <t>Q2 2023</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CoStar property analytics</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>UNDER CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="H7" s="72" t="n"/>
-      <c r="I7" s="72" t="n"/>
+          <t>STABILIZED / STABILIZING</t>
+        </is>
+      </c>
+      <c r="H7" s="72" t="n">
+        <v>0.974453</v>
+      </c>
+      <c r="I7" s="72" t="n">
+        <v>0.996</v>
+      </c>
       <c r="J7" s="72" t="n"/>
-      <c r="K7" s="73" t="n"/>
-      <c r="L7" s="73" t="n"/>
-      <c r="M7" s="73" t="n"/>
-      <c r="N7" s="73" t="n"/>
+      <c r="K7" s="73" t="n">
+        <v>2213</v>
+      </c>
+      <c r="L7" s="73" t="n">
+        <v>2303</v>
+      </c>
+      <c r="M7" s="73" t="n">
+        <v>2147.615759341101</v>
+      </c>
+      <c r="N7" s="73" t="n">
+        <v>2147.615759341101</v>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>CoStar+RealPage</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Diligence: under construction</t>
+          <t>Year built: 2023/2024; Occ: CoStar 97% vs RealPage 100%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>The Quarter at Harris Ranch</t>
+          <t>737 ParkCenter</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3430-3450 S Hopes Well Way, Boise 83716</t>
+          <t>787 E Parkcenter Blvd</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2027</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Q1 2027</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4074,40 +4120,37 @@
       <c r="N8" s="73" t="n"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Diligence</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: under construction</t>
+          <t>Diligence: under construction</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>The Ranahan</t>
+          <t>The Quarter at Harris Ranch</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4227 E Brightside St</t>
+          <t>3430-3450 S Hopes Well Way, Boise 83716</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>138</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2027</v>
+        <v>32</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q1 2027</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
       <c r="H9" s="72" t="n"/>
@@ -4119,32 +4162,35 @@
       <c r="N9" s="73" t="n"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>Diligence</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: under construction</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Seasons on the Bench</t>
+          <t>The Ranahan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2521 W Victory Rd</t>
+          <t>4227 E Brightside St</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>300</v>
+        <v>138</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2027</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Q3 2028</t>
+          <t>Q4 2028</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4161,28 +4207,33 @@
       <c r="N10" s="73" t="n"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>RealPage</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3300 South Vista Avenue</t>
+          <t>Seasons on the Bench</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3300 S Vista Ave</t>
+          <t>2521 W Victory Rd</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>300</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -4210,16 +4261,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1519 South Londoner Avenue</t>
+          <t>3300 South Vista Avenue</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1519 S Londoner Ave</t>
+          <t>3300 S Vista Ave</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -4247,16 +4298,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Station Village</t>
+          <t>1519 South Londoner Avenue</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2350 W Kootenai St</t>
+          <t>1519 S Londoner Ave</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -4284,16 +4335,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Vista Point</t>
+          <t>Station Village</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2017 W Victory Rd</t>
+          <t>2350 W Kootenai St</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>892</v>
+        <v>86</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -4321,16 +4372,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kootenai &amp; Federal Way (Hawkins)</t>
+          <t>Vista Point</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kootenai St &amp; S Federal Way, Boise 83705</t>
+          <t>2017 W Victory Rd</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>194</v>
+        <v>892</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -4346,10 +4397,47 @@
       <c r="N15" s="73" t="n"/>
       <c r="O15" t="inlineStr">
         <is>
+          <t>RealPage</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Kootenai &amp; Federal Way (Hawkins)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kootenai St &amp; S Federal Way, Boise 83705</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>194</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="H16" s="72" t="n"/>
+      <c r="I16" s="72" t="n"/>
+      <c r="J16" s="72" t="n"/>
+      <c r="K16" s="73" t="n"/>
+      <c r="L16" s="73" t="n"/>
+      <c r="M16" s="73" t="n"/>
+      <c r="N16" s="73" t="n"/>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>Diligence</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
         </is>

--- a/CanyonRidge/supply/Canyon_Ridge__Supply_Chart.xlsx
+++ b/CanyonRidge/supply/Canyon_Ridge__Supply_Chart.xlsx
@@ -1236,7 +1236,7 @@
       <c r="B17" s="20" t="n"/>
       <c r="C17" s="21" t="inlineStr">
         <is>
-          <t>PROPOSED (7 properties, 1,982 units)</t>
+          <t>PROPOSED (7 properties, 1,988 units)</t>
         </is>
       </c>
     </row>
@@ -1292,15 +1292,15 @@
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>The Ranahan</t>
+          <t>Kootenai &amp; Federal Way (Hawkins)</t>
         </is>
       </c>
       <c r="D19" s="24" t="n">
-        <v>138</v>
+        <v>200</v>
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q1 2029</t>
         </is>
       </c>
       <c r="F19" s="25" t="n"/>
@@ -1311,20 +1311,16 @@
       </c>
       <c r="H19" s="23" t="inlineStr">
         <is>
-          <t>Dave Evans Construction</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I19" s="27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J19" s="22" t="inlineStr">
-        <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
+        <v>4.1</v>
+      </c>
+      <c r="J19" s="22" t="n"/>
       <c r="K19" s="23" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
         </is>
       </c>
       <c r="M19">
@@ -1370,7 +1366,7 @@
       </c>
       <c r="K20" s="23" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed - stalled; open field 3.5 yrs post-entitlement</t>
         </is>
       </c>
       <c r="M20">
@@ -1384,11 +1380,11 @@
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>Kootenai &amp; Federal Way (Hawkins)</t>
+          <t>1519 South Londoner Avenue</t>
         </is>
       </c>
       <c r="D21" s="24" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
@@ -1407,12 +1403,16 @@
         </is>
       </c>
       <c r="I21" s="27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J21" s="22" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>Garden</t>
+        </is>
+      </c>
       <c r="K21" s="23" t="inlineStr">
         <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed - stalled; litigation-frozen at Idaho Supreme Court</t>
         </is>
       </c>
       <c r="M21">
@@ -1426,11 +1426,11 @@
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>1519 South Londoner Avenue</t>
+          <t>3300 South Vista Avenue</t>
         </is>
       </c>
       <c r="D22" s="24" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
@@ -1449,16 +1449,16 @@
         </is>
       </c>
       <c r="I22" s="27" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J22" s="22" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed - stalled; no financing or permits 16 months post-settlement</t>
         </is>
       </c>
       <c r="M22">
@@ -1472,11 +1472,11 @@
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>3300 South Vista Avenue</t>
+          <t>The Ranahan</t>
         </is>
       </c>
       <c r="D23" s="24" t="n">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="E23" s="22" t="inlineStr">
         <is>
@@ -1491,11 +1491,11 @@
       </c>
       <c r="H23" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Dave Evans Construction</t>
         </is>
       </c>
       <c r="I23" s="27" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J23" s="22" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="K23" s="23" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed - stalled; entitlement shelved - for-sale listing pulled</t>
         </is>
       </c>
       <c r="M23">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="K24" s="23" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed - stalled; 2016 CUP long expired - likely dead</t>
         </is>
       </c>
       <c r="M24">
@@ -1885,9 +1885,13 @@
         </is>
       </c>
       <c r="S12" s="36" t="n">
-        <v>194</v>
-      </c>
-      <c r="T12" s="40" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="T12" s="40" t="inlineStr">
+        <is>
+          <t>Q1 2029</t>
+        </is>
+      </c>
       <c r="U12" s="40" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -1971,11 +1975,7 @@
       <c r="S15" s="36" t="n">
         <v>138</v>
       </c>
-      <c r="T15" s="40" t="inlineStr">
-        <is>
-          <t>Q4 2028</t>
-        </is>
-      </c>
+      <c r="T15" s="40" t="inlineStr"/>
       <c r="U15" s="40" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -4174,23 +4174,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>The Ranahan</t>
+          <t>Kootenai &amp; Federal Way (Hawkins)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4227 E Brightside St</t>
+          <t>Kootenai St &amp; S Federal Way, Boise 83705</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>138</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2027</v>
+        <v>200</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q1 2029</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4207,12 +4204,12 @@
       <c r="N10" s="73" t="n"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>Diligence</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
         </is>
       </c>
     </row>
@@ -4261,17 +4258,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3300 South Vista Avenue</t>
+          <t>The Ranahan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3300 S Vista Ave</t>
+          <t>4227 E Brightside St</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>183</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>PROPOSED</t>
@@ -4286,29 +4287,30 @@
       <c r="N12" s="73" t="n"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>RealPage</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed - stalled; entitlement shelved - for-sale listing pulled</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1519 South Londoner Avenue</t>
+          <t>3300 South Vista Avenue</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1519 S Londoner Ave</t>
+          <t>3300 S Vista Ave</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>189</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>PROPOSED</t>
@@ -4328,24 +4330,25 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed - stalled; no financing or permits 16 months post-settlement</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Station Village</t>
+          <t>1519 South Londoner Avenue</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2350 W Kootenai St</t>
+          <t>1519 S Londoner Ave</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>PROPOSED</t>
@@ -4365,24 +4368,25 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed - stalled; litigation-frozen at Idaho Supreme Court</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Vista Point</t>
+          <t>Station Village</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2017 W Victory Rd</t>
+          <t>2350 W Kootenai St</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>892</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>PROPOSED</t>
@@ -4402,24 +4406,25 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed - stalled; 2016 CUP long expired - likely dead</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kootenai &amp; Federal Way (Hawkins)</t>
+          <t>Vista Point</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kootenai St &amp; S Federal Way, Boise 83705</t>
+          <t>2017 W Victory Rd</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>194</v>
-      </c>
+        <v>892</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>PROPOSED</t>
@@ -4434,12 +4439,12 @@
       <c r="N16" s="73" t="n"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Diligence</t>
+          <t>RealPage</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed - stalled; open field 3.5 yrs post-entitlement</t>
         </is>
       </c>
     </row>
@@ -4522,16 +4527,20 @@
           <t>892</t>
         </is>
       </c>
-      <c r="D4" s="75" t="n"/>
+      <c r="D4" s="75" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="E4" s="35" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed - stalled; open field 3.5 yrs post-entitlement</t>
         </is>
       </c>
       <c r="F4" s="35" t="n"/>
       <c r="G4" s="35" t="inlineStr">
         <is>
-          <t>Welltower's 892-unit plan (25 units income-restricted at 100% AMI; 68-ft height exception) on the eastern Simunich site approved by Boise City Council Feb 2023. As of June 2026 the site remains an open field with Welltower still 'working through its development process' — no construction start, no defensible delivery date.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Welltower's 892-unit plan approved Feb 2023; June 10 2026 Idaho Statesman confirms the site is 'still open fields' with Welltower only 'actively working' its process. No permit in any City of Boise issued-permit report through June 2026; BoiseDev tracker not updated since 2022; absent from BoiseDev's May 2026 construction tour. Bear-only — no defensible delivery date; Welltower still owns and says it's working the deal, so keep alive for re-check.</t>
         </is>
       </c>
       <c r="H4" s="35" t="inlineStr">
@@ -4564,7 +4573,7 @@
       <c r="F5" s="35" t="n"/>
       <c r="G5" s="35" t="inlineStr">
         <is>
-          <t>Original 354-unit MorganStonehill plan (approved 2023) never built and was superseded: Roundhouse re-pitched the site as 'Victory' — 300 garden-style units in 15 buildings at 2521/1251 W Victory Rd targeting a fall 2026 groundbreaking (June 2026 reporting). Q3 2028 = fall 2026 start + ~20 months.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Roundhouse 'The Victory': 300 garden units in 15 bldgs (ten 24-plex, five 12-plex) + 9k sf clubhouse on 18 ac at 2521/1251 W Victory Rd. Building permits FILED (not yet issued) with City of Boise early June 2026; managing director Patrick Boel targets fall 2026 groundbreaking; independently corroborated by Idaho Dept of Labor June 26 2026 regional report. Supersedes MorganStonehill's 354u 'Seasons on the Bench' (2023, never built) — 300u is correct. Q3 2028 delivery defensible. RE-CHECK Oct-Nov 2026: likely promotion to UC on permit issuance/groundbreak.</t>
         </is>
       </c>
       <c r="H5" s="35" t="inlineStr">
@@ -4584,16 +4593,20 @@
           <t>183</t>
         </is>
       </c>
-      <c r="D6" s="75" t="n"/>
+      <c r="D6" s="75" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="E6" s="35" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed - stalled; no financing or permits 16 months post-settlement</t>
         </is>
       </c>
       <c r="F6" s="35" t="n"/>
       <c r="G6" s="35" t="inlineStr">
         <is>
-          <t>Gardner Company phased redevelopment of three aging Vista Ave hotels: ~183 apartments (20% at 100% AMI via density bonus) plus a new 240-room hotel and Hindu temple; council denied the opposition appeal Oct 2023 and the ownership-fraud suit that stalled the project settled March 2025 — no vertical construction as of mid-2026.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Fully entitled (council upheld Oct 2023); both lawsuits resolved (idols Nov 2024, ownership-fraud settled Mar 2025) — but stated next step was 'financing' and nothing has moved since: no demo/building permits at the site through June 2026, BoiseDev tracker stale since Aug 2022, and the Ramada by Wyndham is still open and taking bookings into mid-2026. Bear-only.</t>
         </is>
       </c>
       <c r="H6" s="35" t="inlineStr">
@@ -4613,16 +4626,20 @@
           <t>189</t>
         </is>
       </c>
-      <c r="D7" s="75" t="n"/>
+      <c r="D7" s="75" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="E7" s="35" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed - stalled; litigation-frozen at Idaho Supreme Court</t>
         </is>
       </c>
       <c r="F7" s="35" t="n"/>
       <c r="G7" s="35" t="inlineStr">
         <is>
-          <t>Payette Forward (Austin TX) rezone for 189 units + ground-floor retail on ~6 ac along Highland St approved March 4 2025 (capped at 189 units). Londoner Neighborhood Assn suit dismissed Nov 2025 as untimely but appealed to the Idaho Supreme Court — entitlement upheld, litigation risk remains, no construction.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Entitlement intact (approved Mar 4 2025, capped 189u); neighbors' suit dismissed as untimely Nov 2025 but appealed to the Idaho Supreme Court Dec 2025 — appeal still in briefing, NOT on the argument calendar through Aug 2026. Zero permit/construction activity 16 months post-approval. The Crexi/LoopNet 'for sale' hit is the stale Feb 2021 pre-acquisition land flyer, not a current listing. Bear-only; earliest plausible delivery ~2029 if developer prevails.</t>
         </is>
       </c>
       <c r="H7" s="35" t="inlineStr">
@@ -4642,16 +4659,20 @@
           <t>86</t>
         </is>
       </c>
-      <c r="D8" s="75" t="n"/>
+      <c r="D8" s="75" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="E8" s="35" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed - stalled; 2016 CUP long expired - likely dead</t>
         </is>
       </c>
       <c r="F8" s="35" t="n"/>
       <c r="G8" s="35" t="inlineStr">
         <is>
-          <t>Day Realty Co. plan for 86 units in six buildings + clubhouse at 2350 W Kootenai St; BoiseDev's project tracker has listed it 'on hold' since April 2021 with no subsequent approvals, permits, or news — stale entry, likely dead but unconfirmed. Undated, so not in the forecast. Sits on land-use developable parcel S1015325410.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Primary records confirm likely dead: P&amp;Z approved rezone CAR16-00030 + 91u PUD16-00027 Dec 2016; the 24-month CUP lapsed with NO building permit ever filed at 2350 W Kootenai (City of Boise Housing OpenData, queried 7/16/2026). BoiseDev 'on hold' since Apr 2021, unchanged. Parcel S1015325410 still 6.8 ac bare land but RETAINED R-2 zoning; Day-family Vista Village LLC still active — revival would be a brand-new application with 2+ yr lead. Bear-only shadow, undated.</t>
         </is>
       </c>
       <c r="H8" s="35" t="inlineStr">
@@ -4700,16 +4721,20 @@
           <t>138</t>
         </is>
       </c>
-      <c r="D10" s="75" t="n"/>
+      <c r="D10" s="75" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="E10" s="35" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed - stalled; entitlement shelved - for-sale listing pulled</t>
         </is>
       </c>
       <c r="F10" s="35" t="n"/>
       <c r="G10" s="35" t="inlineStr">
         <is>
-          <t>Entitled 138-unit 4-story project at 4110 E Warm Springs Ave (Harris Ranch / Barber Valley, on land-use developable parcel R1719910020); appeared in city permit logs 2023 but the project/site is now marketed FOR SALE via KW Commercial — no construction, CoStar's Q4 2028 delivery is speculative.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Permits (main bldg + clubhouse/pool) were plan-check COMPLETE and 'ready but not issued' at City of Boise June 2023 — never pulled. Entitled site marketed for sale via KW Commercial (RealNex, 4.50% pro-forma cap); as of 7/16/2026 that listing 302-redirects (taken down), no recorded sale. City Development Tracker + high-impact permit layers show ZERO activity at 4110 E Warm Springs through Jul 2026. Bear-only; shelf-ready plans could revive fast under a buyer — watch item.</t>
         </is>
       </c>
       <c r="H10" s="35" t="inlineStr">
@@ -4788,10 +4813,14 @@
       </c>
       <c r="C13" s="75" t="inlineStr">
         <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="D13" s="75" t="n"/>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D13" s="75" t="inlineStr">
+        <is>
+          <t>Q1 2029</t>
+        </is>
+      </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
           <t>proposed</t>
@@ -4800,7 +4829,7 @@
       <c r="F13" s="35" t="n"/>
       <c r="G13" s="35" t="inlineStr">
         <is>
-          <t>AUDIT FIND: Hawkins Companies (same sponsor as The Judy) — 194 units, 5-story + 2k sf retail + 323 stalls on the triangular Bench lot at Kootenai St &amp; S Federal Way (~4.1 mi). Council approved Feb 2025 (appeal denied); updated design submitted ~Oct 2025; Hawkins said construction 'possibly within a year' (Aug 2025). No building permit through June 2026. Not in CoStar/RealPage.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). UPSIZED: Boise Design Review Commission unanimously approved DRH25-00398 on 12/10/2025 — now SIX stories, 200 units (was 5-story/194u), 319 podium stalls, Pivot North design, at 1095 S Federal Way. Site cleared under Jun 2024 demo permit BLD24-01479. Still NO building permit through June 2026 and Hawkins' own portfolio page omits it — stays PROPOSED. Hawkins said construction 'possibly within a year' (Aug 2025); late-2026/2027 start supports ~Q1 2029 delivery.</t>
         </is>
       </c>
       <c r="H13" s="35" t="inlineStr">
